--- a/assets/sample_metadata/custom_fields_MPXV_metadata_Sample_Run_1.xlsx
+++ b/assets/sample_metadata/custom_fields_MPXV_metadata_Sample_Run_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyoconnell/Desktop/tostadas/assets/sample_metadata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ick4\Downloads\sample_metadata2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE30C83-3DA3-A94D-B624-C6F9541C9F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD81D812-6F34-4184-B232-9F5D6F664FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="13240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MPXV_Metadata" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="448">
   <si>
     <t>Strategy</t>
   </si>
@@ -1373,6 +1373,15 @@
   </si>
   <si>
     <t>gff_path</t>
+  </si>
+  <si>
+    <t>source_type</t>
+  </si>
+  <si>
+    <t>bs-package</t>
+  </si>
+  <si>
+    <t>strain</t>
   </si>
 </sst>
 </file>
@@ -1382,7 +1391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2088,32 +2097,34 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AZ45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BC45"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="24.1640625" customWidth="1"/>
-    <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="15.1640625" customWidth="1"/>
-    <col min="11" max="11" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="23.5" customWidth="1"/>
-    <col min="14" max="15" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="29" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13.5" style="17" customWidth="1"/>
-    <col min="33" max="33" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="34" max="39" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.5" customWidth="1"/>
-    <col min="41" max="49" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="50" max="52" width="13.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="24.1796875" customWidth="1"/>
+    <col min="5" max="5" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="15.1796875" customWidth="1"/>
+    <col min="11" max="11" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="23.453125" customWidth="1"/>
+    <col min="14" max="15" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="13.453125" customWidth="1"/>
+    <col min="27" max="32" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="13.453125" style="17" customWidth="1"/>
+    <col min="36" max="36" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="37" max="42" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.453125" customWidth="1"/>
+    <col min="44" max="52" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="53" max="55" width="13.453125" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:55" ht="18.75" customHeight="1">
       <c r="A1" t="s">
         <v>317</v>
       </c>
@@ -2122,23 +2133,23 @@
       </c>
       <c r="L1" s="46"/>
       <c r="M1" s="46"/>
-      <c r="X1" s="36" t="s">
+      <c r="AA1" s="36" t="s">
         <v>319</v>
       </c>
-      <c r="AB1" s="36" t="s">
+      <c r="AE1" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="AG1" s="36" t="s">
+      <c r="AJ1" s="36" t="s">
         <v>321</v>
       </c>
-      <c r="AH1" s="36" t="s">
+      <c r="AK1" s="36" t="s">
         <v>322</v>
       </c>
-      <c r="AQ1" s="36" t="s">
+      <c r="AT1" s="36" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="2" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:55" ht="18.75" customHeight="1">
       <c r="A2" s="45" t="s">
         <v>441</v>
       </c>
@@ -2208,95 +2219,104 @@
       <c r="W2" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="X2" s="37" t="s">
+      <c r="X2" s="45" t="s">
+        <v>445</v>
+      </c>
+      <c r="Y2" s="45" t="s">
+        <v>447</v>
+      </c>
+      <c r="Z2" s="47" t="s">
+        <v>446</v>
+      </c>
+      <c r="AA2" s="37" t="s">
         <v>231</v>
       </c>
-      <c r="Y2" s="20" t="s">
+      <c r="AB2" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AC2" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="AA2" s="20" t="s">
+      <c r="AD2" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="AB2" s="37" t="s">
+      <c r="AE2" s="37" t="s">
         <v>244</v>
       </c>
-      <c r="AC2" s="20" t="s">
+      <c r="AF2" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="AD2" s="21" t="s">
+      <c r="AG2" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="AE2" s="48" t="s">
+      <c r="AH2" s="48" t="s">
         <v>422</v>
       </c>
-      <c r="AF2" s="48" t="s">
+      <c r="AI2" s="48" t="s">
         <v>444</v>
       </c>
-      <c r="AG2" s="37" t="s">
+      <c r="AJ2" s="37" t="s">
         <v>224</v>
       </c>
-      <c r="AH2" s="37" t="s">
+      <c r="AK2" s="37" t="s">
         <v>288</v>
       </c>
-      <c r="AI2" s="20" t="s">
+      <c r="AL2" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="AJ2" s="20" t="s">
+      <c r="AM2" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="AK2" s="20" t="s">
+      <c r="AN2" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="AL2" s="20" t="s">
+      <c r="AO2" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="AM2" s="20" t="s">
+      <c r="AP2" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="AN2" s="45" t="s">
+      <c r="AQ2" s="45" t="s">
         <v>414</v>
       </c>
-      <c r="AO2" s="45" t="s">
+      <c r="AR2" s="45" t="s">
         <v>298</v>
       </c>
-      <c r="AP2" s="20" t="s">
+      <c r="AS2" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="AQ2" s="37" t="s">
+      <c r="AT2" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="AR2" s="20" t="s">
+      <c r="AU2" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="AS2" s="20" t="s">
+      <c r="AV2" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="AT2" s="20" t="s">
+      <c r="AW2" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="AU2" s="20" t="s">
+      <c r="AX2" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="AV2" s="20" t="s">
+      <c r="AY2" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="AW2" s="20" t="s">
+      <c r="AZ2" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="AX2" s="21" t="s">
+      <c r="BA2" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="AY2" s="21" t="s">
+      <c r="BB2" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="AZ2" s="21" t="s">
+      <c r="BC2" s="21" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:55" ht="18.75" customHeight="1">
       <c r="A3" t="s">
         <v>385</v>
       </c>
@@ -2327,56 +2347,56 @@
       <c r="V3" t="s">
         <v>389</v>
       </c>
-      <c r="X3" s="36"/>
-      <c r="AB3" t="s">
+      <c r="AA3" s="36"/>
+      <c r="AE3" t="s">
         <v>390</v>
       </c>
-      <c r="AD3" s="14">
+      <c r="AG3" s="14">
         <v>40</v>
       </c>
-      <c r="AE3" s="14" t="s">
+      <c r="AH3" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="AF3" s="14"/>
-      <c r="AG3" t="s">
+      <c r="AI3" s="14"/>
+      <c r="AJ3" t="s">
         <v>391</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AK3" t="s">
         <v>216</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AL3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AM3" t="s">
         <v>73</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AN3" t="s">
         <v>85</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AO3" t="s">
         <v>310</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AQ3" t="s">
         <v>415</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AR3" t="s">
         <v>429</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="AS3" t="s">
         <v>434</v>
       </c>
-      <c r="AQ3" s="36"/>
-      <c r="AX3" s="14">
+      <c r="AT3" s="36"/>
+      <c r="BA3" s="14">
         <v>5</v>
       </c>
-      <c r="AY3" s="50" t="s">
+      <c r="BB3" s="50" t="s">
         <v>438</v>
       </c>
-      <c r="AZ3" s="14">
+      <c r="BC3" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:55" ht="18.75" customHeight="1">
       <c r="A4" t="s">
         <v>392</v>
       </c>
@@ -2407,56 +2427,56 @@
       <c r="V4" t="s">
         <v>396</v>
       </c>
-      <c r="X4" s="36"/>
-      <c r="AB4" t="s">
+      <c r="AA4" s="36"/>
+      <c r="AE4" t="s">
         <v>397</v>
       </c>
-      <c r="AD4" s="14">
+      <c r="AG4" s="14">
         <v>121</v>
       </c>
-      <c r="AE4" s="14" t="s">
+      <c r="AH4" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="AF4" s="14"/>
-      <c r="AG4" t="s">
+      <c r="AI4" s="14"/>
+      <c r="AJ4" t="s">
         <v>398</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AK4" t="s">
         <v>216</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AL4" t="s">
         <v>4</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AM4" t="s">
         <v>73</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AN4" t="s">
         <v>85</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AO4" t="s">
         <v>310</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AQ4" t="s">
         <v>415</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AR4" t="s">
         <v>430</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AS4" t="s">
         <v>435</v>
       </c>
-      <c r="AQ4" s="36"/>
-      <c r="AX4" s="14">
+      <c r="AT4" s="36"/>
+      <c r="BA4" s="14">
         <v>8</v>
       </c>
-      <c r="AY4" s="49" t="s">
+      <c r="BB4" s="49" t="s">
         <v>439</v>
       </c>
-      <c r="AZ4" s="14">
+      <c r="BC4" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:55" ht="18.75" customHeight="1">
       <c r="A5" t="s">
         <v>399</v>
       </c>
@@ -2490,56 +2510,56 @@
       <c r="V5" t="s">
         <v>401</v>
       </c>
-      <c r="X5" s="36"/>
-      <c r="AB5" t="s">
+      <c r="AA5" s="36"/>
+      <c r="AE5" t="s">
         <v>402</v>
       </c>
-      <c r="AD5" s="14">
+      <c r="AG5" s="14">
         <v>72</v>
       </c>
-      <c r="AE5" s="14" t="s">
+      <c r="AH5" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="AF5" s="14"/>
-      <c r="AG5" t="s">
+      <c r="AI5" s="14"/>
+      <c r="AJ5" t="s">
         <v>403</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AK5" t="s">
         <v>216</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AL5" t="s">
         <v>4</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AM5" t="s">
         <v>73</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AN5" t="s">
         <v>85</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AO5" t="s">
         <v>310</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AQ5" t="s">
         <v>415</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AR5" t="s">
         <v>431</v>
       </c>
-      <c r="AP5" t="s">
+      <c r="AS5" t="s">
         <v>436</v>
       </c>
-      <c r="AQ5" s="36"/>
-      <c r="AX5" s="14">
+      <c r="AT5" s="36"/>
+      <c r="BA5" s="14">
         <v>4</v>
       </c>
-      <c r="AY5" s="50" t="s">
+      <c r="BB5" s="50" t="s">
         <v>440</v>
       </c>
-      <c r="AZ5" s="14">
+      <c r="BC5" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:55" ht="18.75" customHeight="1">
       <c r="A6" t="s">
         <v>442</v>
       </c>
@@ -2573,56 +2593,56 @@
       <c r="V6" t="s">
         <v>381</v>
       </c>
-      <c r="X6" s="36"/>
-      <c r="AB6" t="s">
+      <c r="AA6" s="36"/>
+      <c r="AE6" t="s">
         <v>407</v>
       </c>
-      <c r="AD6" s="14">
+      <c r="AG6" s="14">
         <v>73</v>
       </c>
-      <c r="AE6" s="14" t="s">
+      <c r="AH6" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="AF6" s="14"/>
-      <c r="AG6" t="s">
+      <c r="AI6" s="14"/>
+      <c r="AJ6" t="s">
         <v>408</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AK6" t="s">
         <v>216</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AL6" t="s">
         <v>4</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AM6" t="s">
         <v>73</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AN6" t="s">
         <v>85</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AO6" t="s">
         <v>310</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AQ6" t="s">
         <v>415</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AR6" t="s">
         <v>432</v>
       </c>
-      <c r="AP6" t="s">
+      <c r="AS6" t="s">
         <v>437</v>
       </c>
-      <c r="AQ6" s="36"/>
-      <c r="AX6" s="17" t="s">
+      <c r="AT6" s="36"/>
+      <c r="BA6" s="17" t="s">
         <v>409</v>
       </c>
-      <c r="AY6" s="50" t="s">
+      <c r="BB6" s="50" t="s">
         <v>406</v>
       </c>
-      <c r="AZ6" s="14">
+      <c r="BC6" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:55" ht="18.75" customHeight="1">
       <c r="A7" t="s">
         <v>443</v>
       </c>
@@ -2656,431 +2676,431 @@
       <c r="V7" t="s">
         <v>381</v>
       </c>
-      <c r="X7" s="36"/>
-      <c r="AB7" t="s">
+      <c r="AA7" s="36"/>
+      <c r="AE7" t="s">
         <v>382</v>
       </c>
-      <c r="AD7" s="14">
+      <c r="AG7" s="14">
         <v>247</v>
       </c>
-      <c r="AE7" s="49" t="s">
+      <c r="AH7" s="49" t="s">
         <v>423</v>
       </c>
-      <c r="AF7" s="49"/>
-      <c r="AG7" t="s">
+      <c r="AI7" s="49"/>
+      <c r="AJ7" t="s">
         <v>383</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AK7" t="s">
         <v>216</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AL7" t="s">
         <v>4</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AM7" t="s">
         <v>73</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AN7" t="s">
         <v>85</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AO7" t="s">
         <v>310</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AQ7" t="s">
         <v>415</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AR7" t="s">
         <v>428</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AS7" t="s">
         <v>433</v>
       </c>
-      <c r="AQ7" s="36"/>
-      <c r="AX7" s="14" t="s">
+      <c r="AT7" s="36"/>
+      <c r="BA7" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="AY7" s="17" t="s">
+      <c r="BB7" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="AZ7" s="14">
+      <c r="BC7" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="X8" s="36"/>
-      <c r="AD8" s="14"/>
-      <c r="AE8" s="14"/>
-      <c r="AF8" s="14"/>
-      <c r="AQ8" s="36"/>
-    </row>
-    <row r="9" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:55" ht="18.75" customHeight="1">
+      <c r="AA8" s="36"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
+      <c r="AT8" s="36"/>
+    </row>
+    <row r="9" spans="1:55" ht="18.75" customHeight="1">
       <c r="K9" s="36"/>
       <c r="L9" s="46"/>
       <c r="M9" s="46"/>
-      <c r="X9" s="36"/>
-      <c r="AB9" s="36"/>
-      <c r="AG9" s="36"/>
-      <c r="AH9" s="36"/>
-      <c r="AQ9" s="36"/>
-    </row>
-    <row r="10" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA9" s="36"/>
+      <c r="AE9" s="36"/>
+      <c r="AJ9" s="36"/>
+      <c r="AK9" s="36"/>
+      <c r="AT9" s="36"/>
+    </row>
+    <row r="10" spans="1:55" ht="18.75" customHeight="1">
       <c r="K10" s="36"/>
       <c r="L10" s="46"/>
       <c r="M10" s="46"/>
-      <c r="X10" s="36"/>
-      <c r="AB10" s="36"/>
-      <c r="AG10" s="36"/>
-      <c r="AH10" s="36"/>
-      <c r="AQ10" s="36"/>
-    </row>
-    <row r="11" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA10" s="36"/>
+      <c r="AE10" s="36"/>
+      <c r="AJ10" s="36"/>
+      <c r="AK10" s="36"/>
+      <c r="AT10" s="36"/>
+    </row>
+    <row r="11" spans="1:55" ht="18.75" customHeight="1">
       <c r="K11" s="36"/>
       <c r="L11" s="46"/>
       <c r="M11" s="46"/>
-      <c r="X11" s="36"/>
-      <c r="AB11" s="36"/>
-      <c r="AG11" s="36"/>
-      <c r="AH11" s="36"/>
-      <c r="AQ11" s="36"/>
-    </row>
-    <row r="12" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA11" s="36"/>
+      <c r="AE11" s="36"/>
+      <c r="AJ11" s="36"/>
+      <c r="AK11" s="36"/>
+      <c r="AT11" s="36"/>
+    </row>
+    <row r="12" spans="1:55" ht="18.75" customHeight="1">
       <c r="K12" s="36"/>
       <c r="L12" s="46"/>
       <c r="M12" s="46"/>
-      <c r="X12" s="36"/>
-      <c r="AB12" s="36"/>
-      <c r="AG12" s="36"/>
-      <c r="AH12" s="36"/>
-      <c r="AQ12" s="36"/>
-    </row>
-    <row r="13" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA12" s="36"/>
+      <c r="AE12" s="36"/>
+      <c r="AJ12" s="36"/>
+      <c r="AK12" s="36"/>
+      <c r="AT12" s="36"/>
+    </row>
+    <row r="13" spans="1:55" ht="18.75" customHeight="1">
       <c r="K13" s="36"/>
       <c r="L13" s="46"/>
       <c r="M13" s="46"/>
-      <c r="X13" s="36"/>
-      <c r="AB13" s="36"/>
-      <c r="AG13" s="36"/>
-      <c r="AH13" s="36"/>
-      <c r="AQ13" s="36"/>
-    </row>
-    <row r="14" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA13" s="36"/>
+      <c r="AE13" s="36"/>
+      <c r="AJ13" s="36"/>
+      <c r="AK13" s="36"/>
+      <c r="AT13" s="36"/>
+    </row>
+    <row r="14" spans="1:55" ht="18.75" customHeight="1">
       <c r="K14" s="36"/>
       <c r="L14" s="46"/>
       <c r="M14" s="46"/>
-      <c r="X14" s="36"/>
-      <c r="AB14" s="36"/>
-      <c r="AG14" s="36"/>
-      <c r="AH14" s="36"/>
-      <c r="AQ14" s="36"/>
-    </row>
-    <row r="15" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA14" s="36"/>
+      <c r="AE14" s="36"/>
+      <c r="AJ14" s="36"/>
+      <c r="AK14" s="36"/>
+      <c r="AT14" s="36"/>
+    </row>
+    <row r="15" spans="1:55" ht="18.75" customHeight="1">
       <c r="K15" s="36"/>
       <c r="L15" s="46"/>
       <c r="M15" s="46"/>
-      <c r="X15" s="36"/>
-      <c r="AB15" s="36"/>
-      <c r="AG15" s="36"/>
-      <c r="AH15" s="36"/>
-      <c r="AQ15" s="36"/>
-    </row>
-    <row r="16" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA15" s="36"/>
+      <c r="AE15" s="36"/>
+      <c r="AJ15" s="36"/>
+      <c r="AK15" s="36"/>
+      <c r="AT15" s="36"/>
+    </row>
+    <row r="16" spans="1:55" ht="18.75" customHeight="1">
       <c r="K16" s="36"/>
       <c r="L16" s="46"/>
       <c r="M16" s="46"/>
-      <c r="X16" s="36"/>
-      <c r="AB16" s="36"/>
-      <c r="AG16" s="36"/>
-      <c r="AH16" s="36"/>
-      <c r="AQ16" s="36"/>
-    </row>
-    <row r="17" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA16" s="36"/>
+      <c r="AE16" s="36"/>
+      <c r="AJ16" s="36"/>
+      <c r="AK16" s="36"/>
+      <c r="AT16" s="36"/>
+    </row>
+    <row r="17" spans="11:46" ht="18.75" customHeight="1">
       <c r="K17" s="36"/>
       <c r="L17" s="46"/>
       <c r="M17" s="46"/>
-      <c r="X17" s="36"/>
-      <c r="AB17" s="36"/>
-      <c r="AG17" s="36"/>
-      <c r="AH17" s="36"/>
-      <c r="AQ17" s="36"/>
-    </row>
-    <row r="18" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA17" s="36"/>
+      <c r="AE17" s="36"/>
+      <c r="AJ17" s="36"/>
+      <c r="AK17" s="36"/>
+      <c r="AT17" s="36"/>
+    </row>
+    <row r="18" spans="11:46" ht="18.75" customHeight="1">
       <c r="K18" s="36"/>
       <c r="L18" s="46"/>
       <c r="M18" s="46"/>
-      <c r="X18" s="36"/>
-      <c r="AB18" s="36"/>
-      <c r="AG18" s="36"/>
-      <c r="AH18" s="36"/>
-      <c r="AQ18" s="36"/>
-    </row>
-    <row r="19" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA18" s="36"/>
+      <c r="AE18" s="36"/>
+      <c r="AJ18" s="36"/>
+      <c r="AK18" s="36"/>
+      <c r="AT18" s="36"/>
+    </row>
+    <row r="19" spans="11:46" ht="18.75" customHeight="1">
       <c r="K19" s="36"/>
       <c r="L19" s="46"/>
       <c r="M19" s="46"/>
-      <c r="X19" s="36"/>
-      <c r="AB19" s="36"/>
-      <c r="AG19" s="36"/>
-      <c r="AH19" s="36"/>
-      <c r="AQ19" s="36"/>
-    </row>
-    <row r="20" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA19" s="36"/>
+      <c r="AE19" s="36"/>
+      <c r="AJ19" s="36"/>
+      <c r="AK19" s="36"/>
+      <c r="AT19" s="36"/>
+    </row>
+    <row r="20" spans="11:46" ht="18.75" customHeight="1">
       <c r="K20" s="36"/>
       <c r="L20" s="46"/>
       <c r="M20" s="46"/>
-      <c r="X20" s="36"/>
-      <c r="AB20" s="36"/>
-      <c r="AG20" s="36"/>
-      <c r="AH20" s="36"/>
-      <c r="AQ20" s="36"/>
-    </row>
-    <row r="21" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA20" s="36"/>
+      <c r="AE20" s="36"/>
+      <c r="AJ20" s="36"/>
+      <c r="AK20" s="36"/>
+      <c r="AT20" s="36"/>
+    </row>
+    <row r="21" spans="11:46" ht="18.75" customHeight="1">
       <c r="K21" s="36"/>
       <c r="L21" s="46"/>
       <c r="M21" s="46"/>
-      <c r="X21" s="36"/>
-      <c r="AB21" s="36"/>
-      <c r="AG21" s="36"/>
-      <c r="AH21" s="36"/>
-      <c r="AQ21" s="36"/>
-    </row>
-    <row r="22" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA21" s="36"/>
+      <c r="AE21" s="36"/>
+      <c r="AJ21" s="36"/>
+      <c r="AK21" s="36"/>
+      <c r="AT21" s="36"/>
+    </row>
+    <row r="22" spans="11:46" ht="18.75" customHeight="1">
       <c r="K22" s="36"/>
       <c r="L22" s="46"/>
       <c r="M22" s="46"/>
-      <c r="X22" s="36"/>
-      <c r="AB22" s="36"/>
-      <c r="AG22" s="36"/>
-      <c r="AH22" s="36"/>
-      <c r="AQ22" s="36"/>
-    </row>
-    <row r="23" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA22" s="36"/>
+      <c r="AE22" s="36"/>
+      <c r="AJ22" s="36"/>
+      <c r="AK22" s="36"/>
+      <c r="AT22" s="36"/>
+    </row>
+    <row r="23" spans="11:46" ht="18.75" customHeight="1">
       <c r="K23" s="36"/>
       <c r="L23" s="46"/>
       <c r="M23" s="46"/>
-      <c r="X23" s="36"/>
-      <c r="AB23" s="36"/>
-      <c r="AG23" s="36"/>
-      <c r="AH23" s="36"/>
-      <c r="AQ23" s="36"/>
-    </row>
-    <row r="24" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA23" s="36"/>
+      <c r="AE23" s="36"/>
+      <c r="AJ23" s="36"/>
+      <c r="AK23" s="36"/>
+      <c r="AT23" s="36"/>
+    </row>
+    <row r="24" spans="11:46" ht="18.75" customHeight="1">
       <c r="K24" s="36"/>
       <c r="L24" s="46"/>
       <c r="M24" s="46"/>
-      <c r="X24" s="36"/>
-      <c r="AB24" s="36"/>
-      <c r="AG24" s="36"/>
-      <c r="AH24" s="36"/>
-      <c r="AQ24" s="36"/>
-    </row>
-    <row r="25" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA24" s="36"/>
+      <c r="AE24" s="36"/>
+      <c r="AJ24" s="36"/>
+      <c r="AK24" s="36"/>
+      <c r="AT24" s="36"/>
+    </row>
+    <row r="25" spans="11:46" ht="18.75" customHeight="1">
       <c r="K25" s="36"/>
       <c r="L25" s="46"/>
       <c r="M25" s="46"/>
-      <c r="X25" s="36"/>
-      <c r="AB25" s="36"/>
-      <c r="AG25" s="36"/>
-      <c r="AH25" s="36"/>
-      <c r="AQ25" s="36"/>
-    </row>
-    <row r="26" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA25" s="36"/>
+      <c r="AE25" s="36"/>
+      <c r="AJ25" s="36"/>
+      <c r="AK25" s="36"/>
+      <c r="AT25" s="36"/>
+    </row>
+    <row r="26" spans="11:46" ht="18.75" customHeight="1">
       <c r="K26" s="36"/>
       <c r="L26" s="46"/>
       <c r="M26" s="46"/>
-      <c r="X26" s="36"/>
-      <c r="AB26" s="36"/>
-      <c r="AG26" s="36"/>
-      <c r="AH26" s="36"/>
-      <c r="AQ26" s="36"/>
-    </row>
-    <row r="27" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA26" s="36"/>
+      <c r="AE26" s="36"/>
+      <c r="AJ26" s="36"/>
+      <c r="AK26" s="36"/>
+      <c r="AT26" s="36"/>
+    </row>
+    <row r="27" spans="11:46" ht="18.75" customHeight="1">
       <c r="K27" s="36"/>
       <c r="L27" s="46"/>
       <c r="M27" s="46"/>
-      <c r="X27" s="36"/>
-      <c r="AB27" s="36"/>
-      <c r="AG27" s="36"/>
-      <c r="AH27" s="36"/>
-      <c r="AQ27" s="36"/>
-    </row>
-    <row r="28" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA27" s="36"/>
+      <c r="AE27" s="36"/>
+      <c r="AJ27" s="36"/>
+      <c r="AK27" s="36"/>
+      <c r="AT27" s="36"/>
+    </row>
+    <row r="28" spans="11:46" ht="18.75" customHeight="1">
       <c r="K28" s="36"/>
       <c r="L28" s="46"/>
       <c r="M28" s="46"/>
-      <c r="X28" s="36"/>
-      <c r="AB28" s="36"/>
-      <c r="AG28" s="36"/>
-      <c r="AH28" s="36"/>
-      <c r="AQ28" s="36"/>
-    </row>
-    <row r="29" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA28" s="36"/>
+      <c r="AE28" s="36"/>
+      <c r="AJ28" s="36"/>
+      <c r="AK28" s="36"/>
+      <c r="AT28" s="36"/>
+    </row>
+    <row r="29" spans="11:46" ht="18.75" customHeight="1">
       <c r="K29" s="36"/>
       <c r="L29" s="46"/>
       <c r="M29" s="46"/>
-      <c r="X29" s="36"/>
-      <c r="AB29" s="36"/>
-      <c r="AG29" s="36"/>
-      <c r="AH29" s="36"/>
-      <c r="AQ29" s="36"/>
-    </row>
-    <row r="30" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA29" s="36"/>
+      <c r="AE29" s="36"/>
+      <c r="AJ29" s="36"/>
+      <c r="AK29" s="36"/>
+      <c r="AT29" s="36"/>
+    </row>
+    <row r="30" spans="11:46" ht="18.75" customHeight="1">
       <c r="K30" s="36"/>
       <c r="L30" s="46"/>
       <c r="M30" s="46"/>
-      <c r="X30" s="36"/>
-      <c r="AB30" s="36"/>
-      <c r="AG30" s="36"/>
-      <c r="AH30" s="36"/>
-      <c r="AQ30" s="36"/>
-    </row>
-    <row r="31" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA30" s="36"/>
+      <c r="AE30" s="36"/>
+      <c r="AJ30" s="36"/>
+      <c r="AK30" s="36"/>
+      <c r="AT30" s="36"/>
+    </row>
+    <row r="31" spans="11:46" ht="18.75" customHeight="1">
       <c r="K31" s="36"/>
       <c r="L31" s="46"/>
       <c r="M31" s="46"/>
-      <c r="X31" s="36"/>
-      <c r="AB31" s="36"/>
-      <c r="AG31" s="36"/>
-      <c r="AH31" s="36"/>
-      <c r="AQ31" s="36"/>
-    </row>
-    <row r="32" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA31" s="36"/>
+      <c r="AE31" s="36"/>
+      <c r="AJ31" s="36"/>
+      <c r="AK31" s="36"/>
+      <c r="AT31" s="36"/>
+    </row>
+    <row r="32" spans="11:46" ht="18.75" customHeight="1">
       <c r="K32" s="36"/>
       <c r="L32" s="46"/>
       <c r="M32" s="46"/>
-      <c r="X32" s="36"/>
-      <c r="AB32" s="36"/>
-      <c r="AG32" s="36"/>
-      <c r="AH32" s="36"/>
-      <c r="AQ32" s="36"/>
-    </row>
-    <row r="33" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA32" s="36"/>
+      <c r="AE32" s="36"/>
+      <c r="AJ32" s="36"/>
+      <c r="AK32" s="36"/>
+      <c r="AT32" s="36"/>
+    </row>
+    <row r="33" spans="11:46" ht="18.75" customHeight="1">
       <c r="K33" s="36"/>
       <c r="L33" s="46"/>
       <c r="M33" s="46"/>
-      <c r="X33" s="36"/>
-      <c r="AB33" s="36"/>
-      <c r="AG33" s="36"/>
-      <c r="AH33" s="36"/>
-      <c r="AQ33" s="36"/>
-    </row>
-    <row r="34" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA33" s="36"/>
+      <c r="AE33" s="36"/>
+      <c r="AJ33" s="36"/>
+      <c r="AK33" s="36"/>
+      <c r="AT33" s="36"/>
+    </row>
+    <row r="34" spans="11:46" ht="18.75" customHeight="1">
       <c r="K34" s="36"/>
       <c r="L34" s="46"/>
       <c r="M34" s="46"/>
-      <c r="X34" s="36"/>
-      <c r="AB34" s="36"/>
-      <c r="AG34" s="36"/>
-      <c r="AH34" s="36"/>
-      <c r="AQ34" s="36"/>
-    </row>
-    <row r="35" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA34" s="36"/>
+      <c r="AE34" s="36"/>
+      <c r="AJ34" s="36"/>
+      <c r="AK34" s="36"/>
+      <c r="AT34" s="36"/>
+    </row>
+    <row r="35" spans="11:46" ht="18.75" customHeight="1">
       <c r="K35" s="36"/>
       <c r="L35" s="46"/>
       <c r="M35" s="46"/>
-      <c r="X35" s="36"/>
-      <c r="AB35" s="36"/>
-      <c r="AG35" s="36"/>
-      <c r="AH35" s="36"/>
-      <c r="AQ35" s="36"/>
-    </row>
-    <row r="36" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA35" s="36"/>
+      <c r="AE35" s="36"/>
+      <c r="AJ35" s="36"/>
+      <c r="AK35" s="36"/>
+      <c r="AT35" s="36"/>
+    </row>
+    <row r="36" spans="11:46" ht="18.75" customHeight="1">
       <c r="K36" s="36"/>
       <c r="L36" s="46"/>
       <c r="M36" s="46"/>
-      <c r="X36" s="36"/>
-      <c r="AB36" s="36"/>
-      <c r="AG36" s="36"/>
-      <c r="AH36" s="36"/>
-      <c r="AQ36" s="36"/>
-    </row>
-    <row r="37" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA36" s="36"/>
+      <c r="AE36" s="36"/>
+      <c r="AJ36" s="36"/>
+      <c r="AK36" s="36"/>
+      <c r="AT36" s="36"/>
+    </row>
+    <row r="37" spans="11:46" ht="18.75" customHeight="1">
       <c r="K37" s="36"/>
       <c r="L37" s="46"/>
       <c r="M37" s="46"/>
-      <c r="X37" s="36"/>
-      <c r="AB37" s="36"/>
-      <c r="AG37" s="36"/>
-      <c r="AH37" s="36"/>
-      <c r="AQ37" s="36"/>
-    </row>
-    <row r="38" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA37" s="36"/>
+      <c r="AE37" s="36"/>
+      <c r="AJ37" s="36"/>
+      <c r="AK37" s="36"/>
+      <c r="AT37" s="36"/>
+    </row>
+    <row r="38" spans="11:46" ht="18.75" customHeight="1">
       <c r="K38" s="36"/>
       <c r="L38" s="46"/>
       <c r="M38" s="46"/>
-      <c r="X38" s="36"/>
-      <c r="AB38" s="36"/>
-      <c r="AG38" s="36"/>
-      <c r="AH38" s="36"/>
-      <c r="AQ38" s="36"/>
-    </row>
-    <row r="39" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA38" s="36"/>
+      <c r="AE38" s="36"/>
+      <c r="AJ38" s="36"/>
+      <c r="AK38" s="36"/>
+      <c r="AT38" s="36"/>
+    </row>
+    <row r="39" spans="11:46" ht="18.75" customHeight="1">
       <c r="K39" s="36"/>
       <c r="L39" s="46"/>
       <c r="M39" s="46"/>
-      <c r="X39" s="36"/>
-      <c r="AB39" s="36"/>
-      <c r="AG39" s="36"/>
-      <c r="AH39" s="36"/>
-      <c r="AQ39" s="36"/>
-    </row>
-    <row r="40" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA39" s="36"/>
+      <c r="AE39" s="36"/>
+      <c r="AJ39" s="36"/>
+      <c r="AK39" s="36"/>
+      <c r="AT39" s="36"/>
+    </row>
+    <row r="40" spans="11:46" ht="18.75" customHeight="1">
       <c r="K40" s="36"/>
       <c r="L40" s="46"/>
       <c r="M40" s="46"/>
-      <c r="X40" s="36"/>
-      <c r="AB40" s="36"/>
-      <c r="AG40" s="36"/>
-      <c r="AH40" s="36"/>
-      <c r="AQ40" s="36"/>
-    </row>
-    <row r="41" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA40" s="36"/>
+      <c r="AE40" s="36"/>
+      <c r="AJ40" s="36"/>
+      <c r="AK40" s="36"/>
+      <c r="AT40" s="36"/>
+    </row>
+    <row r="41" spans="11:46" ht="18.75" customHeight="1">
       <c r="K41" s="36"/>
       <c r="L41" s="46"/>
       <c r="M41" s="46"/>
-      <c r="X41" s="36"/>
-      <c r="AB41" s="36"/>
-      <c r="AG41" s="36"/>
-      <c r="AH41" s="36"/>
-      <c r="AQ41" s="36"/>
-    </row>
-    <row r="42" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA41" s="36"/>
+      <c r="AE41" s="36"/>
+      <c r="AJ41" s="36"/>
+      <c r="AK41" s="36"/>
+      <c r="AT41" s="36"/>
+    </row>
+    <row r="42" spans="11:46" ht="18.75" customHeight="1">
       <c r="K42" s="36"/>
       <c r="L42" s="46"/>
       <c r="M42" s="46"/>
-      <c r="X42" s="36"/>
-      <c r="AB42" s="36"/>
-      <c r="AG42" s="36"/>
-      <c r="AH42" s="36"/>
-      <c r="AQ42" s="36"/>
-    </row>
-    <row r="43" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA42" s="36"/>
+      <c r="AE42" s="36"/>
+      <c r="AJ42" s="36"/>
+      <c r="AK42" s="36"/>
+      <c r="AT42" s="36"/>
+    </row>
+    <row r="43" spans="11:46" ht="18.75" customHeight="1">
       <c r="K43" s="36"/>
       <c r="L43" s="46"/>
       <c r="M43" s="46"/>
-      <c r="X43" s="36"/>
-      <c r="AB43" s="36"/>
-      <c r="AG43" s="36"/>
-      <c r="AH43" s="36"/>
-      <c r="AQ43" s="36"/>
-    </row>
-    <row r="44" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA43" s="36"/>
+      <c r="AE43" s="36"/>
+      <c r="AJ43" s="36"/>
+      <c r="AK43" s="36"/>
+      <c r="AT43" s="36"/>
+    </row>
+    <row r="44" spans="11:46" ht="18.75" customHeight="1">
       <c r="K44" s="36"/>
       <c r="L44" s="46"/>
       <c r="M44" s="46"/>
-      <c r="X44" s="36"/>
-      <c r="AB44" s="36"/>
-      <c r="AG44" s="36"/>
-      <c r="AH44" s="36"/>
-      <c r="AQ44" s="36"/>
-    </row>
-    <row r="45" spans="11:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA44" s="36"/>
+      <c r="AE44" s="36"/>
+      <c r="AJ44" s="36"/>
+      <c r="AK44" s="36"/>
+      <c r="AT44" s="36"/>
+    </row>
+    <row r="45" spans="11:46" ht="18.75" customHeight="1">
       <c r="K45" s="36"/>
       <c r="L45" s="46"/>
       <c r="M45" s="46"/>
-      <c r="X45" s="36"/>
-      <c r="AB45" s="36"/>
-      <c r="AG45" s="36"/>
-      <c r="AH45" s="36"/>
-      <c r="AQ45" s="36"/>
+      <c r="AA45" s="36"/>
+      <c r="AE45" s="36"/>
+      <c r="AJ45" s="36"/>
+      <c r="AK45" s="36"/>
+      <c r="AT45" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3094,27 +3114,27 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AI30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="35" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.81640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="35" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="18.75" customHeight="1">
       <c r="A1" t="s">
         <v>317</v>
       </c>
@@ -3137,7 +3157,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" ht="18.75" customHeight="1">
       <c r="A2" s="20" t="s">
         <v>222</v>
       </c>
@@ -3244,7 +3264,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" ht="18.75" customHeight="1">
       <c r="A3" t="s">
         <v>330</v>
       </c>
@@ -3345,7 +3365,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" ht="18.75" customHeight="1">
       <c r="A4" t="s">
         <v>339</v>
       </c>
@@ -3443,7 +3463,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" ht="18.75" customHeight="1">
       <c r="D5" s="36"/>
       <c r="M5" s="36"/>
       <c r="Q5" s="36"/>
@@ -3451,7 +3471,7 @@
       <c r="U5" s="36"/>
       <c r="AC5" s="36"/>
     </row>
-    <row r="6" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="18.75" customHeight="1">
       <c r="D6" s="36"/>
       <c r="M6" s="36"/>
       <c r="Q6" s="36"/>
@@ -3459,7 +3479,7 @@
       <c r="U6" s="36"/>
       <c r="AC6" s="36"/>
     </row>
-    <row r="7" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" ht="18.75" customHeight="1">
       <c r="D7" s="36"/>
       <c r="M7" s="36"/>
       <c r="Q7" s="36"/>
@@ -3467,7 +3487,7 @@
       <c r="U7" s="36"/>
       <c r="AC7" s="36"/>
     </row>
-    <row r="8" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="18.75" customHeight="1">
       <c r="A8" s="39" t="s">
         <v>341</v>
       </c>
@@ -3480,7 +3500,7 @@
       <c r="U8" s="36"/>
       <c r="AC8" s="36"/>
     </row>
-    <row r="9" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="18.75" customHeight="1">
       <c r="A9" t="s">
         <v>317</v>
       </c>
@@ -3503,7 +3523,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="18.75" customHeight="1">
       <c r="A10" s="20" t="s">
         <v>222</v>
       </c>
@@ -3610,7 +3630,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" ht="18.75" customHeight="1">
       <c r="A11" t="s">
         <v>330</v>
       </c>
@@ -3658,7 +3678,7 @@
       <c r="U11" s="36"/>
       <c r="AC11" s="36"/>
     </row>
-    <row r="12" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" ht="18.75" customHeight="1">
       <c r="A12" t="s">
         <v>342</v>
       </c>
@@ -3700,7 +3720,7 @@
       <c r="U12" s="36"/>
       <c r="AC12" s="36"/>
     </row>
-    <row r="13" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="18.75" customHeight="1">
       <c r="D13" s="36"/>
       <c r="M13" s="36"/>
       <c r="Q13" s="36"/>
@@ -3708,7 +3728,7 @@
       <c r="U13" s="36"/>
       <c r="AC13" s="36"/>
     </row>
-    <row r="14" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" ht="18.75" customHeight="1">
       <c r="A14" s="39" t="s">
         <v>347</v>
       </c>
@@ -3721,7 +3741,7 @@
       <c r="U14" s="36"/>
       <c r="AC14" s="36"/>
     </row>
-    <row r="15" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" ht="18.75" customHeight="1">
       <c r="A15" t="s">
         <v>317</v>
       </c>
@@ -3744,7 +3764,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" ht="18.75" customHeight="1">
       <c r="A16" s="20" t="s">
         <v>222</v>
       </c>
@@ -3851,7 +3871,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" ht="18.75" customHeight="1">
       <c r="A17" t="s">
         <v>348</v>
       </c>
@@ -3930,7 +3950,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" ht="18.75" customHeight="1">
       <c r="A18" t="s">
         <v>357</v>
       </c>
@@ -3992,7 +4012,7 @@
       </c>
       <c r="AC18" s="36"/>
     </row>
-    <row r="19" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" ht="18.75" customHeight="1">
       <c r="A19" t="s">
         <v>362</v>
       </c>
@@ -4042,7 +4062,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" ht="18.75" customHeight="1">
       <c r="D20" s="36"/>
       <c r="M20" s="36"/>
       <c r="Q20" s="36"/>
@@ -4050,7 +4070,7 @@
       <c r="U20" s="36"/>
       <c r="AC20" s="36"/>
     </row>
-    <row r="21" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" ht="18.75" customHeight="1">
       <c r="D21" s="36"/>
       <c r="M21" s="36"/>
       <c r="Q21" s="36"/>
@@ -4058,7 +4078,7 @@
       <c r="U21" s="36"/>
       <c r="AC21" s="36"/>
     </row>
-    <row r="22" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" ht="18.75" customHeight="1">
       <c r="D22" s="36"/>
       <c r="M22" s="36"/>
       <c r="Q22" s="36"/>
@@ -4066,7 +4086,7 @@
       <c r="U22" s="36"/>
       <c r="AC22" s="36"/>
     </row>
-    <row r="23" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" ht="18.75" customHeight="1">
       <c r="A23" s="41"/>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
@@ -4083,7 +4103,7 @@
       <c r="U23" s="36"/>
       <c r="AC23" s="36"/>
     </row>
-    <row r="24" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="18.75" customHeight="1">
       <c r="A24" s="41"/>
       <c r="B24" s="44" t="s">
         <v>367</v>
@@ -4102,7 +4122,7 @@
       <c r="U24" s="36"/>
       <c r="AC24" s="36"/>
     </row>
-    <row r="25" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" ht="18.75" customHeight="1">
       <c r="A25" s="41"/>
       <c r="B25" s="41"/>
       <c r="C25" s="41"/>
@@ -4119,7 +4139,7 @@
       <c r="U25" s="36"/>
       <c r="AC25" s="36"/>
     </row>
-    <row r="26" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" ht="18.75" customHeight="1">
       <c r="A26" s="41"/>
       <c r="B26" s="41"/>
       <c r="C26" s="41"/>
@@ -4136,7 +4156,7 @@
       <c r="U26" s="36"/>
       <c r="AC26" s="36"/>
     </row>
-    <row r="27" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" ht="18.75" customHeight="1">
       <c r="A27" s="41"/>
       <c r="B27" s="41"/>
       <c r="C27" s="41"/>
@@ -4153,7 +4173,7 @@
       <c r="U27" s="36"/>
       <c r="AC27" s="36"/>
     </row>
-    <row r="28" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" ht="18.75" customHeight="1">
       <c r="D28" s="36"/>
       <c r="M28" s="36"/>
       <c r="Q28" s="36"/>
@@ -4161,7 +4181,7 @@
       <c r="U28" s="36"/>
       <c r="AC28" s="36"/>
     </row>
-    <row r="29" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" ht="18.75" customHeight="1">
       <c r="D29" s="36"/>
       <c r="M29" s="36"/>
       <c r="Q29" s="36"/>
@@ -4169,7 +4189,7 @@
       <c r="U29" s="36"/>
       <c r="AC29" s="36"/>
     </row>
-    <row r="30" spans="1:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:35" ht="18.75" customHeight="1">
       <c r="D30" s="36"/>
       <c r="M30" s="36"/>
       <c r="Q30" s="36"/>
@@ -4188,30 +4208,30 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AN2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="29" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="37" max="39" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="29" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="37" max="39" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" ht="18.75" customHeight="1">
       <c r="A1" s="20" t="s">
         <v>222</v>
       </c>
@@ -4333,7 +4353,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" ht="18.75" customHeight="1">
       <c r="A2" s="24" t="s">
         <v>301</v>
       </c>
@@ -4463,24 +4483,24 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="21" max="31" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" style="18" bestFit="1" customWidth="1"/>
+    <col min="21" max="31" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1">
       <c r="A1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1">
       <c r="A2" t="s">
         <v>222</v>
       </c>
@@ -4575,7 +4595,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="18.75" customHeight="1">
       <c r="A3" t="s">
         <v>278</v>
       </c>
@@ -4658,7 +4678,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" ht="18.75" customHeight="1">
       <c r="O4" s="19"/>
     </row>
   </sheetData>
@@ -4672,20 +4692,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="31" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="31" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1">
       <c r="A1" t="s">
         <v>222</v>
       </c>
@@ -4780,7 +4800,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1">
       <c r="A2" t="s">
         <v>253</v>
       </c>
@@ -4886,22 +4906,22 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K107"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
@@ -4914,7 +4934,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="18.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -4931,7 +4951,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="18.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4948,7 +4968,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="18.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -4965,7 +4985,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -4982,7 +5002,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="18.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -4999,7 +5019,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="18.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -5016,7 +5036,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="18.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -5033,7 +5053,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="18.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -5050,7 +5070,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="18.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -5067,7 +5087,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="18.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -5084,7 +5104,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="18.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -5101,7 +5121,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="18.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -5118,7 +5138,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="18.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -5135,7 +5155,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="18.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -5152,7 +5172,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="18.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -5169,7 +5189,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="18.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -5186,7 +5206,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="18.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -5203,7 +5223,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="18.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
@@ -5220,7 +5240,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="18.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
@@ -5237,7 +5257,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="18.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -5254,7 +5274,7 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="18.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
@@ -5271,7 +5291,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="18.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
@@ -5288,7 +5308,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="18.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
@@ -5305,7 +5325,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="18.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>46</v>
       </c>
@@ -5320,7 +5340,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="18.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>47</v>
       </c>
@@ -5337,7 +5357,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="18.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>49</v>
       </c>
@@ -5354,7 +5374,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="18.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>51</v>
       </c>
@@ -5371,7 +5391,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="18.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>53</v>
       </c>
@@ -5388,7 +5408,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="18.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>55</v>
       </c>
@@ -5405,7 +5425,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="18.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>57</v>
       </c>
@@ -5420,7 +5440,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="18.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>58</v>
       </c>
@@ -5437,7 +5457,7 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="18.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>60</v>
       </c>
@@ -5454,7 +5474,7 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
     </row>
-    <row r="34" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="18.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>62</v>
       </c>
@@ -5471,7 +5491,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="18.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>64</v>
       </c>
@@ -5486,7 +5506,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="18.75" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>65</v>
       </c>
@@ -5501,7 +5521,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="18.75" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>66</v>
       </c>
@@ -5518,7 +5538,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="18.75" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="51"/>
       <c r="C38" s="51"/>
@@ -5531,7 +5551,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="18.75" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>68</v>
       </c>
@@ -5548,7 +5568,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="18.75" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>69</v>
       </c>
@@ -5565,7 +5585,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="18.75" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>71</v>
       </c>
@@ -5582,7 +5602,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
-    <row r="42" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="18.75" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>73</v>
       </c>
@@ -5599,7 +5619,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
-    <row r="43" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="18.75" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>75</v>
       </c>
@@ -5616,7 +5636,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="18.75" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>77</v>
       </c>
@@ -5633,7 +5653,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="18.75" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>79</v>
       </c>
@@ -5650,7 +5670,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="18.75" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>81</v>
       </c>
@@ -5665,7 +5685,7 @@
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
     </row>
-    <row r="47" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="18.75" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>82</v>
       </c>
@@ -5680,7 +5700,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
     </row>
-    <row r="48" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="18.75" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>66</v>
       </c>
@@ -5697,7 +5717,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
-    <row r="49" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="18.75" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="51"/>
       <c r="C49" s="51"/>
@@ -5710,7 +5730,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="18.75" customHeight="1">
       <c r="A50" s="3" t="s">
         <v>84</v>
       </c>
@@ -5727,7 +5747,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" ht="18.75" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>85</v>
       </c>
@@ -5744,7 +5764,7 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
     </row>
-    <row r="52" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="18.75" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>87</v>
       </c>
@@ -5761,7 +5781,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
     </row>
-    <row r="53" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="18.75" customHeight="1">
       <c r="A53" s="1" t="s">
         <v>89</v>
       </c>
@@ -5778,7 +5798,7 @@
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
     </row>
-    <row r="54" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="18.75" customHeight="1">
       <c r="A54" s="1" t="s">
         <v>91</v>
       </c>
@@ -5795,7 +5815,7 @@
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
     </row>
-    <row r="55" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="18.75" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>93</v>
       </c>
@@ -5812,7 +5832,7 @@
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
     </row>
-    <row r="56" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="18.75" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>95</v>
       </c>
@@ -5829,7 +5849,7 @@
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
     </row>
-    <row r="57" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="18.75" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>97</v>
       </c>
@@ -5846,7 +5866,7 @@
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
     </row>
-    <row r="58" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="18.75" customHeight="1">
       <c r="A58" s="1" t="s">
         <v>99</v>
       </c>
@@ -5863,7 +5883,7 @@
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
     </row>
-    <row r="59" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" ht="18.75" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>101</v>
       </c>
@@ -5880,7 +5900,7 @@
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
     </row>
-    <row r="60" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" ht="18.75" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>103</v>
       </c>
@@ -5897,7 +5917,7 @@
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
     </row>
-    <row r="61" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="18.75" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>105</v>
       </c>
@@ -5914,7 +5934,7 @@
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
     </row>
-    <row r="62" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="18.75" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>107</v>
       </c>
@@ -5931,7 +5951,7 @@
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="18.75" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>109</v>
       </c>
@@ -5948,7 +5968,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
     </row>
-    <row r="64" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="18.75" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>111</v>
       </c>
@@ -5965,7 +5985,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="18.75" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>113</v>
       </c>
@@ -5982,7 +6002,7 @@
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
     </row>
-    <row r="66" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="18.75" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>115</v>
       </c>
@@ -5999,7 +6019,7 @@
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
     </row>
-    <row r="67" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" ht="18.75" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>117</v>
       </c>
@@ -6016,7 +6036,7 @@
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
     </row>
-    <row r="68" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" ht="18.75" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>119</v>
       </c>
@@ -6033,7 +6053,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
-    <row r="69" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" ht="18.75" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>121</v>
       </c>
@@ -6050,7 +6070,7 @@
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
     </row>
-    <row r="70" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" ht="18.75" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>123</v>
       </c>
@@ -6067,7 +6087,7 @@
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
     </row>
-    <row r="71" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" ht="18.75" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>125</v>
       </c>
@@ -6084,7 +6104,7 @@
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
     </row>
-    <row r="72" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" ht="18.75" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>127</v>
       </c>
@@ -6101,7 +6121,7 @@
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
     </row>
-    <row r="73" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="18.75" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>129</v>
       </c>
@@ -6118,7 +6138,7 @@
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
     </row>
-    <row r="74" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="18.75" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>131</v>
       </c>
@@ -6135,7 +6155,7 @@
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
     </row>
-    <row r="75" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" ht="18.75" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>133</v>
       </c>
@@ -6152,7 +6172,7 @@
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
     </row>
-    <row r="76" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" ht="18.75" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>135</v>
       </c>
@@ -6169,7 +6189,7 @@
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" ht="18.75" customHeight="1">
       <c r="A77" s="1" t="s">
         <v>137</v>
       </c>
@@ -6186,7 +6206,7 @@
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" ht="18.75" customHeight="1">
       <c r="A78" s="1" t="s">
         <v>139</v>
       </c>
@@ -6201,7 +6221,7 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" ht="18.75" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>140</v>
       </c>
@@ -6216,7 +6236,7 @@
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" ht="18.75" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>141</v>
       </c>
@@ -6233,7 +6253,7 @@
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" ht="18.75" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>143</v>
       </c>
@@ -6250,7 +6270,7 @@
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
     </row>
-    <row r="82" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" ht="18.75" customHeight="1">
       <c r="A82" s="1" t="s">
         <v>145</v>
       </c>
@@ -6267,7 +6287,7 @@
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
     </row>
-    <row r="83" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" ht="18.75" customHeight="1">
       <c r="A83" s="1" t="s">
         <v>147</v>
       </c>
@@ -6284,7 +6304,7 @@
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
     </row>
-    <row r="84" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" ht="18.75" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="2"/>
@@ -6297,7 +6317,7 @@
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
     </row>
-    <row r="85" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" ht="18.75" customHeight="1">
       <c r="A85" s="3" t="s">
         <v>149</v>
       </c>
@@ -6312,7 +6332,7 @@
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
     </row>
-    <row r="86" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" ht="18.75" customHeight="1">
       <c r="A86" s="1" t="s">
         <v>150</v>
       </c>
@@ -6347,7 +6367,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" ht="18.75" customHeight="1">
       <c r="A87" s="1" t="s">
         <v>153</v>
       </c>
@@ -6382,7 +6402,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" ht="18.75" customHeight="1">
       <c r="A88" s="1" t="s">
         <v>159</v>
       </c>
@@ -6413,7 +6433,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="18.75" customHeight="1">
       <c r="A89" s="1" t="s">
         <v>157</v>
       </c>
@@ -6444,7 +6464,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="18.75" customHeight="1">
       <c r="A90" s="1" t="s">
         <v>154</v>
       </c>
@@ -6473,7 +6493,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" ht="18.75" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>152</v>
       </c>
@@ -6498,7 +6518,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" ht="18.75" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>151</v>
       </c>
@@ -6521,7 +6541,7 @@
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
     </row>
-    <row r="93" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" ht="18.75" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>156</v>
       </c>
@@ -6542,7 +6562,7 @@
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
     </row>
-    <row r="94" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" ht="18.75" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>158</v>
       </c>
@@ -6561,7 +6581,7 @@
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
     </row>
-    <row r="95" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" ht="18.75" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>155</v>
       </c>
@@ -6580,7 +6600,7 @@
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
     </row>
-    <row r="96" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" ht="18.75" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
@@ -6597,7 +6617,7 @@
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
     </row>
-    <row r="97" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ht="18.75" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
@@ -6612,7 +6632,7 @@
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
     </row>
-    <row r="98" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" ht="18.75" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
@@ -6627,7 +6647,7 @@
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
     </row>
-    <row r="99" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" ht="18.75" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2" t="s">
@@ -6642,7 +6662,7 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
     </row>
-    <row r="100" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" ht="18.75" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="2"/>
       <c r="C100" s="8" t="s">
@@ -6657,7 +6677,7 @@
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
     </row>
-    <row r="101" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" ht="18.75" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="7" t="s">
@@ -6672,7 +6692,7 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
     </row>
-    <row r="102" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ht="18.75" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
@@ -6687,7 +6707,7 @@
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
     </row>
-    <row r="103" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" ht="18.75" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
@@ -6702,7 +6722,7 @@
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
     </row>
-    <row r="104" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" ht="18.75" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
@@ -6717,7 +6737,7 @@
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
     </row>
-    <row r="105" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" ht="18.75" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="2"/>
       <c r="C105" s="1" t="s">
@@ -6732,7 +6752,7 @@
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
     </row>
-    <row r="106" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" ht="18.75" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="2"/>
       <c r="C106" s="1" t="s">
@@ -6747,7 +6767,7 @@
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
     </row>
-    <row r="107" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" ht="18.75" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="2"/>
       <c r="C107" s="1" t="s">
